--- a/DocFile/Sheet/MilestoneSheet.xlsx
+++ b/DocFile/Sheet/MilestoneSheet.xlsx
@@ -1,34 +1,160 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\My Work\Python\Integrating invoice\DocFile\Sheet\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15190" windowHeight="4190"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Responsibility</t>
+  </si>
+  <si>
+    <t>Milestone</t>
+  </si>
+  <si>
+    <t>Visitor’s Visa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	●	Providing a detailed checklist of documents 
+	●	Gathering Documents 
+	●	Help Drafting Submission Letters and Other Documents 
+	●	Review
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	●	Prepare the application 
+	●	Final Review 
+	●	One final consultation, if needed 
+	●	Submit the application 
+</t>
+  </si>
+  <si>
+    <t>Study Permit</t>
+  </si>
+  <si>
+    <t>Spouse sponsorship Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	●	Providing a detailed checklist of documents 
+	●	Gathering Documents 
+	●	Help Drafting Submission Letters and Other Documents 
+	●	Review 
+</t>
+  </si>
+  <si>
+    <t>Humanitarian &amp; Compassionate Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	●	Providing a detailed checklist of documents 
+	●	Gathering Documents 
+	●	Help Drafting Submission Document 
+	●	Review 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	●	Prepare the application 
+	●	Commence the Affidavit 
+	●	Final Review 
+	●	One final consultation, if needed 
+	●	Submit the application 
+</t>
+  </si>
+  <si>
+    <t>Passport Scan Copy - Current and Previous (All pages with seal or visa)
+NID - Translated into English
+Birth Certificate
+Bank Statement: (6 months/ 1 Year) Ensure sufficient funds are available.
+Other Financial Documents 
+Admission/ Offer Letter 
+Official Language Proof 
+Statement of Purpose 
+Resume 
+Relationship documents 
+Travel Itinerary 
+Proof of Experiences  
+Income Proof 
+All documents translated into English 
+Provide any relevant document and information upon request</t>
+  </si>
+  <si>
+    <t>Passport Scan Copy - Current and Previous (All pages with seal or visa)
+NID - Translated into English
+Birth Certificate
+Bank Statement: (6 months/ 1 Year) Ensure sufficient funds are available.
+Other Financial Documents 
+Submission Letter 
+Invitation Letter, if applicable 
+Relationship documents 
+Travel Itinerary and Proof of Accommodation
+Proof of Employment or Business 
+Inome Proof 
+All documents translated into English 
+Provide any relevant document and information upon request</t>
+  </si>
+  <si>
+    <t>For Spouse: 
+Passport Scan Copy - Current and Previous (All pages with seal or visa)
+Support Letter from family members e.g. parents, siblings, friends, etc. as needed.  
+Marriage Documents 
+Canadian Bank Statement (last six months) and good standing letter   
+Employment Letter and Proof of Income
+Police Clearance Certificate (from all countries, if stayed for more than 6 months in the last 10 years)   
+All documentation in English or French, or with an English or French translation with notarization 
+Wedding Ceremony photos (Maximum 20). 
+Any other required documents and information 
+For the Primary Applicant: 
+Passport Scan Copy - Current and Previous (All pages with seal or visa)
+Financial Documents 
+Police Clearance Certificate (from all countries, if stayed for more than 6 months in the last 10 years)   
+Dependent’s information and documents, if applicable</t>
+  </si>
+  <si>
+    <t>Passport Scan Copy - Current and Previous (All pages with seal or visa)
+Support Letter from family members e.g. parents, siblings, friends, etc. as needed.  
+Marriage Documents 
+Canadian Bank Statement (last six months) and good standing letter  
+Other Financial Documents   
+Volunteering Experiences 
+Relevant reports and documents 
+Police Clearance Certificate (from all countries, if stayed for more than 6 months in the last 10 years)   
+All documentation in English or French, or with an English or French translation with notarization 
+Any other required documents and information</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +172,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,29 +482,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="92.6328125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="8.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Responsibility</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
